--- a/wms-vue3/public/templates/plastic-box-import-template.xlsx
+++ b/wms-vue3/public/templates/plastic-box-import-template.xlsx
@@ -413,12 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -437,6 +438,11 @@
           <t>备注</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>指定长度</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -454,6 +460,11 @@
           <t>示例备注（选填，可留空）</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12.50（选填，可留空）</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -464,6 +475,11 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>PBOX-0002（上传前请删除本行示例）</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>25（选填，可留空）</t>
         </is>
       </c>
     </row>

--- a/wms-vue3/public/templates/plastic-box-import-template.xlsx
+++ b/wms-vue3/public/templates/plastic-box-import-template.xlsx
@@ -413,13 +413,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -438,11 +437,6 @@
           <t>备注</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>指定长度</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -460,11 +454,6 @@
           <t>示例备注（选填，可留空）</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12.50（选填，可留空）</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -475,11 +464,6 @@
       <c r="B3" t="inlineStr">
         <is>
           <t>PBOX-0002（上传前请删除本行示例）</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>25（选填，可留空）</t>
         </is>
       </c>
     </row>
